--- a/测试集/边缘情况/样式丰富.xlsx
+++ b/测试集/边缘情况/样式丰富.xlsx
@@ -502,26 +502,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南京新视野广告工作室</t>
+          <t>北京中科联合实业有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HT-6585</t>
+          <t>HT-7956</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>23130.68</v>
+        <v>35573.53</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>16923.42</v>
+        <v>31734.73</v>
       </c>
       <c r="F2" t="n">
-        <v>6207.26</v>
+        <v>3838.8</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
@@ -531,26 +531,26 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46279</v>
+        <v>46236</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>北京中科联合实业有限公司</t>
+          <t>深圳市恒信电子有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HT-3447</t>
+          <t>HT-6038</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>98355.74000000001</v>
+        <v>24564.29</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>72525.98</v>
+        <v>24204.59</v>
       </c>
       <c r="F3" t="n">
-        <v>25829.76</v>
+        <v>359.7</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
@@ -560,26 +560,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>武汉江城建材经营部</t>
+          <t>北京中科联合实业有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HT-3145</t>
+          <t>HT-6978</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>75390.8</v>
+        <v>47235.29</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>74271.3</v>
+        <v>44422.88</v>
       </c>
       <c r="F4" t="n">
-        <v>1119.5</v>
+        <v>2812.41</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
@@ -589,26 +589,26 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46289</v>
+        <v>46245</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>上海岚图贸易有限公司</t>
+          <t>广州云图文化传媒有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HT-8238</t>
+          <t>HT-6229</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>21857.04</v>
+        <v>149767.45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19796.48</v>
+        <v>108243.35</v>
       </c>
       <c r="F5" t="n">
-        <v>2060.56</v>
+        <v>41524.1</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -618,26 +618,26 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>上海岚图贸易有限公司</t>
+          <t>北京中科联合实业有限公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HT-1770</t>
+          <t>HT-9581</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>83676.75</v>
+        <v>72892.47</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>69840.47</v>
+        <v>64472.12</v>
       </c>
       <c r="F6" t="n">
-        <v>13836.28</v>
+        <v>8420.35</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46243</v>
+        <v>46239</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -656,17 +656,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HT-9929</t>
+          <t>HT-9639</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>69963.17</v>
+        <v>35554.7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>57960.63</v>
+        <v>29358.16</v>
       </c>
       <c r="F7" t="n">
-        <v>12002.54</v>
+        <v>6196.54</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -676,26 +676,26 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>深圳市恒信电子有限公司</t>
+          <t>北京中科联合实业有限公司</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HT-1179</t>
+          <t>HT-8237</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>87644.53999999999</v>
+        <v>77933.82000000001</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>72515.63</v>
+        <v>64219.23</v>
       </c>
       <c r="F8" t="n">
-        <v>15128.91</v>
+        <v>13714.59</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -714,17 +714,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HT-8121</t>
+          <t>HT-6100</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>138196.5</v>
+        <v>32773.1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>121716.88</v>
+        <v>30951.92</v>
       </c>
       <c r="F9" t="n">
-        <v>16479.62</v>
+        <v>1821.18</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -734,26 +734,26 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46281</v>
+        <v>46235</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>上海岚图贸易有限公司</t>
+          <t>北京中科联合实业有限公司</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HT-7725</t>
+          <t>HT-6531</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>127455.8</v>
+        <v>24769.01</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>115788.33</v>
+        <v>21844.37</v>
       </c>
       <c r="F10" t="n">
-        <v>11667.47</v>
+        <v>2924.64</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46268</v>
+        <v>46250</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -772,17 +772,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HT-7994</t>
+          <t>HT-7651</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>141180.68</v>
+        <v>113970.36</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>102332.28</v>
+        <v>104670.55</v>
       </c>
       <c r="F11" t="n">
-        <v>38848.4</v>
+        <v>9299.809999999999</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
